--- a/contact_forms/029_real_estate_contact_form--contact_forms.xlsx
+++ b/contact_forms/029_real_estate_contact_form--contact_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -688,8 +688,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -717,12 +717,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'call',_'label':_'call'}</t>
+          <t>call</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Call', 'label': 'Call'}</t>
+          <t>Call</t>
         </is>
       </c>
     </row>
@@ -734,12 +734,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'email',_'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Email', 'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -751,12 +751,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'message',_'label':_'message'}</t>
+          <t>message</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Message', 'label': 'Message'}</t>
+          <t>Message</t>
         </is>
       </c>
     </row>
@@ -768,12 +768,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'pool',_'label':_'pool'}</t>
+          <t>pool</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Pool', 'label': 'Pool'}</t>
+          <t>Pool</t>
         </is>
       </c>
     </row>
@@ -785,12 +785,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'parking',_'label':_'parking'}</t>
+          <t>parking</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Parking', 'label': 'Parking'}</t>
+          <t>Parking</t>
         </is>
       </c>
     </row>
@@ -802,12 +802,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'balcony',_'label':_'balcony'}</t>
+          <t>balcony</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Balcony', 'label': 'Balcony'}</t>
+          <t>Balcony</t>
         </is>
       </c>
     </row>
@@ -819,12 +819,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'gym',_'label':_'gym'}</t>
+          <t>gym</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Gym', 'label': 'Gym'}</t>
+          <t>Gym</t>
         </is>
       </c>
     </row>
@@ -836,12 +836,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'playground',_'label':_'playground'}</t>
+          <t>playground</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Playground', 'label': 'Playground'}</t>
+          <t>Playground</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'garden',_'label':_'garden'}</t>
+          <t>garden</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Garden', 'label': 'Garden'}</t>
+          <t>Garden</t>
         </is>
       </c>
     </row>
